--- a/BWI/bestwine_output/bestwine_Rwanda.xlsx
+++ b/BWI/bestwine_output/bestwine_Rwanda.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1433,6 +1433,79 @@
       <c r="Z10" s="4" t="inlineStr"/>
       <c r="AA10" s="4" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Westgate Limited</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Westgate Limited</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>120120</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Kigali</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Kigali City, Kicukiro</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>KK 698 Street</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://westgateafrica.com</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>rwanda@westgateafrica.com</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Ajith Kumar</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Rwanda.xlsx
+++ b/BWI/bestwine_output/bestwine_Rwanda.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1506,6 +1506,79 @@
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Westgate Limited</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Westgate Limited</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>120120</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Kigali</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Kigali City, Kicukiro</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>KK 698 Street</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://westgateafrica.com</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>rwanda@westgateafrica.com</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Ajith Kumar</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
